--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_coquimbo.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:24</t>
+    <t xml:space="preserve">2026-09-09 20:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2018_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2018_coquimbo.xlsx
@@ -24,51 +24,51 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">La Serena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coquimbo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Andacollo</t>
   </si>
   <si>
+    <t xml:space="preserve">La Higuera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vicuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Illapel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canela</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Vilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ovalle</t>
+  </si>
+  <si>
     <t xml:space="preserve">Combarbalá</t>
   </si>
   <si>
-    <t xml:space="preserve">Coquimbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Higuera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Serena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Vilos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Monte Patria</t>
   </si>
   <si>
-    <t xml:space="preserve">Ovalle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paiguano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Salamanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicuña</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:21</t>
+    <t xml:space="preserve">2026-09-18 10:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>76.38</v>
+        <v>76.33</v>
       </c>
     </row>
     <row r="3">
@@ -498,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>72.92</v>
+        <v>75.18</v>
       </c>
     </row>
     <row r="4">
@@ -506,7 +506,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>73.32</v>
+        <v>76.38</v>
       </c>
     </row>
     <row r="5">
@@ -514,7 +514,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>75.18</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="6">
@@ -522,7 +522,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>75.41</v>
+        <v>73.96</v>
       </c>
     </row>
     <row r="7">
@@ -530,7 +530,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>71.53</v>
+        <v>73.57</v>
       </c>
     </row>
     <row r="8">
@@ -538,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>76.33</v>
+        <v>75.41</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>70.83</v>
+        <v>72.92</v>
       </c>
     </row>
     <row r="10">
@@ -554,7 +554,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>70.31</v>
+        <v>70.83</v>
       </c>
     </row>
     <row r="11">
@@ -562,7 +562,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>73.12</v>
+        <v>74.24</v>
       </c>
     </row>
     <row r="12">
@@ -570,7 +570,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>73.96</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="13">
@@ -578,7 +578,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>71.5</v>
+        <v>73.32</v>
       </c>
     </row>
     <row r="14">
@@ -586,7 +586,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>72.17</v>
+        <v>70.31</v>
       </c>
     </row>
     <row r="15">
@@ -594,7 +594,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>74.24</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="16">
@@ -602,7 +602,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>73.57</v>
+        <v>72.17</v>
       </c>
     </row>
   </sheetData>
